--- a/sample-questions.xlsx
+++ b/sample-questions.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Questions" sheetId="1" r:id="rId1"/>
+    <sheet name="ImageQuestions" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:K11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,27 +407,30 @@
         <v>question</v>
       </c>
       <c r="C1" t="str">
+        <v>question_image</v>
+      </c>
+      <c r="D1" t="str">
         <v>option_a</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>option_b</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>option_c</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>option_d</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>correct_answer</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>points</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>time_limit_seconds</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>category</v>
       </c>
     </row>
@@ -436,31 +439,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Which protocol is used to secure browsing on the World Wide Web?</v>
+        <v>Which of the following is the official logo of the Python programming language?</v>
       </c>
       <c r="C2" t="str">
-        <v>HTTP</v>
+        <v/>
       </c>
       <c r="D2" t="str">
-        <v>HTTPS</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/c/c3/Python-logo-notext.svg</v>
       </c>
       <c r="E2" t="str">
-        <v>FTP</v>
+        <v>https://upload.wikimedia.org/wikipedia/en/3/30/Java_programming_language_logo.svg</v>
       </c>
       <c r="F2" t="str">
-        <v>SSH</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/6/6a/JavaScript-logo.png</v>
       </c>
       <c r="G2" t="str">
-        <v>HTTPS</v>
-      </c>
-      <c r="H2">
+        <v>https://upload.wikimedia.org/wikipedia/commons/2/27/PHP-logo.svg</v>
+      </c>
+      <c r="H2" t="str">
+        <v>A</v>
+      </c>
+      <c r="I2">
         <v>10</v>
       </c>
-      <c r="I2">
-        <v>20</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Cyber Security</v>
+      <c r="J2">
+        <v>20</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Programming Languages</v>
       </c>
     </row>
     <row r="3">
@@ -468,31 +474,34 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Which data structure follows the LIFO (Last-In-First-Out) principle?</v>
+        <v>Which of these is the official mascot of the Linux operating system (Tux)?</v>
       </c>
       <c r="C3" t="str">
-        <v>Queue</v>
+        <v/>
       </c>
       <c r="D3" t="str">
-        <v>Tree</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/f/fa/Apple_logo_black.svg</v>
       </c>
       <c r="E3" t="str">
-        <v>Stack</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/3/35/Tux.svg</v>
       </c>
       <c r="F3" t="str">
-        <v>Graph</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/8/87/Windows_logo_-_2021.svg</v>
       </c>
       <c r="G3" t="str">
-        <v>Stack</v>
-      </c>
-      <c r="H3">
+        <v>https://upload.wikimedia.org/wikipedia/commons/d/d7/Android_robot.svg</v>
+      </c>
+      <c r="H3" t="str">
+        <v>B</v>
+      </c>
+      <c r="I3">
         <v>10</v>
       </c>
-      <c r="I3">
-        <v>20</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Data Structures</v>
+      <c r="J3">
+        <v>20</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Operating Systems</v>
       </c>
     </row>
     <row r="4">
@@ -500,30 +509,33 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>What does CSS stand for in web development?</v>
+        <v>Which of the following is the official logo of the React library?</v>
       </c>
       <c r="C4" t="str">
-        <v>Cascading Style Sheets</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>Creative Style Software</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/9/95/Vue.js_Logo_2.svg</v>
       </c>
       <c r="E4" t="str">
-        <v>Computer System Syntax</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/c/cf/Angular_full_color_logo.svg</v>
       </c>
       <c r="F4" t="str">
-        <v>Control Sheet Syntax</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/a/a7/React-icon.svg</v>
       </c>
       <c r="G4" t="str">
-        <v>Cascading Style Sheets</v>
-      </c>
-      <c r="H4">
+        <v>https://upload.wikimedia.org/wikipedia/commons/1/1b/Svelte_Logo.svg</v>
+      </c>
+      <c r="H4" t="str">
+        <v>C</v>
+      </c>
+      <c r="I4">
         <v>10</v>
       </c>
-      <c r="I4">
-        <v>20</v>
-      </c>
-      <c r="J4" t="str">
+      <c r="J4">
+        <v>20</v>
+      </c>
+      <c r="K4" t="str">
         <v>Web Tech</v>
       </c>
     </row>
@@ -532,31 +544,34 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>What is the binary representation of decimal number 10?</v>
+        <v>Identify the logo of the Git version control system:</v>
       </c>
       <c r="C5" t="str">
-        <v>1001</v>
+        <v/>
       </c>
       <c r="D5" t="str">
-        <v>1010</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/e/e0/Git-logo.svg</v>
       </c>
       <c r="E5" t="str">
-        <v>1100</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/4/4e/Docker_%28container_engine%29_logo.svg</v>
       </c>
       <c r="F5" t="str">
-        <v>1110</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/3/39/Kubernetes_logo_without_workmark.svg</v>
       </c>
       <c r="G5" t="str">
-        <v>1010</v>
-      </c>
-      <c r="H5">
-        <v>15</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/e/e9/Jenkins_logo.svg</v>
+      </c>
+      <c r="H5" t="str">
+        <v>A</v>
       </c>
       <c r="I5">
-        <v>20</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Computer Science</v>
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <v>20</v>
+      </c>
+      <c r="K5" t="str">
+        <v>DevOps &amp; Tools</v>
       </c>
     </row>
     <row r="6">
@@ -564,36 +579,214 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Which company originally developed the Android operating system?</v>
+        <v>Look at the logo below. Which containerization platform does it represent?</v>
       </c>
       <c r="C6" t="str">
-        <v>Apple</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/4/4e/Docker_%28container_engine%29_logo.svg</v>
       </c>
       <c r="D6" t="str">
-        <v>Google</v>
+        <v>Docker</v>
       </c>
       <c r="E6" t="str">
-        <v>Android Inc.</v>
+        <v>Podman</v>
       </c>
       <c r="F6" t="str">
-        <v>Microsoft</v>
+        <v>VirtualBox</v>
       </c>
       <c r="G6" t="str">
-        <v>Android Inc.</v>
-      </c>
-      <c r="H6">
-        <v>20</v>
+        <v>VMware</v>
+      </c>
+      <c r="H6" t="str">
+        <v>A</v>
       </c>
       <c r="I6">
-        <v>20</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Tech Trivia</v>
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Cloud &amp; DevOps</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Which of the following is the logo of PostgreSQL (Elephant)?</v>
+      </c>
+      <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/en/d/dd/MySQL_logo.svg</v>
+      </c>
+      <c r="E7" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/9/93/MongoDB_Logo.svg</v>
+      </c>
+      <c r="F7" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/en/6/6b/Redis_Logo.svg</v>
+      </c>
+      <c r="G7" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/2/29/Postgresql_elephant.svg</v>
+      </c>
+      <c r="H7" t="str">
+        <v>D</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Databases</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Identify the modern programming language represented by this mascot (Ferris):</v>
+      </c>
+      <c r="C8" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/0/0f/Original_Ferris.svg</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Rust</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Golang</v>
+      </c>
+      <c r="F8" t="str">
+        <v>C++</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Zig</v>
+      </c>
+      <c r="H8" t="str">
+        <v>A</v>
+      </c>
+      <c r="I8">
+        <v>15</v>
+      </c>
+      <c r="J8">
+        <v>20</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Programming Languages</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Which of the following is the official logo of GitHub (Octocat)?</v>
+      </c>
+      <c r="C9" t="str">
+        <v/>
+      </c>
+      <c r="D9" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/e/e1/GitLab_logo.svg</v>
+      </c>
+      <c r="E9" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/9/91/Octicons-mark-github.svg</v>
+      </c>
+      <c r="F9" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/0/0e/Bitbucket-blue-logomark-only.svg</v>
+      </c>
+      <c r="G9" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/0/02/Stack_Overflow_logo.svg</v>
+      </c>
+      <c r="H9" t="str">
+        <v>B</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Developer Platforms</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Which popular JavaScript runtime uses this hexagonal green logo?</v>
+      </c>
+      <c r="C10" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/d/d9/Node.js_logo.svg</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Deno</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Node.js</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Bun</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Electron</v>
+      </c>
+      <c r="H10" t="str">
+        <v>B</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+      <c r="J10">
+        <v>20</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Web Tech</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Which of the following is the official cryptocurrency logo of Ethereum?</v>
+      </c>
+      <c r="C11" t="str">
+        <v/>
+      </c>
+      <c r="D11" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/4/46/Bitcoin.svg</v>
+      </c>
+      <c r="E11" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/0/05/Ethereum_logo_2014.svg</v>
+      </c>
+      <c r="F11" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/e/e9/Solana_logo.svg</v>
+      </c>
+      <c r="G11" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/en/d/d0/Dogecoin_Logo.png</v>
+      </c>
+      <c r="H11" t="str">
+        <v>B</v>
+      </c>
+      <c r="I11">
+        <v>15</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Blockchain &amp; Web3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sample-questions.xlsx
+++ b/sample-questions.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="ImageQuestions" sheetId="1" r:id="rId1"/>
+    <sheet name="Questions" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,40 +397,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>round_number</v>
       </c>
       <c r="B1" t="str">
+        <v>difficulty</v>
+      </c>
+      <c r="C1" t="str">
         <v>question</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>question_image</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>option_a</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>option_b</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>option_c</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>option_d</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>correct_answer</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>points</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>time_limit_seconds</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>category</v>
       </c>
     </row>
@@ -439,34 +442,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Which of the following is the official logo of the Python programming language?</v>
+        <v>introduction</v>
       </c>
       <c r="C2" t="str">
+        <v>What does CPU stand for?</v>
+      </c>
+      <c r="D2" t="str">
         <v/>
       </c>
-      <c r="D2" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/c/c3/Python-logo-notext.svg</v>
-      </c>
       <c r="E2" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/en/3/30/Java_programming_language_logo.svg</v>
+        <v>Central Processing Unit</v>
       </c>
       <c r="F2" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/6/6a/JavaScript-logo.png</v>
+        <v>Computer Personal Unit</v>
       </c>
       <c r="G2" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/2/27/PHP-logo.svg</v>
+        <v>Central Power Unit</v>
       </c>
       <c r="H2" t="str">
+        <v>Core Processing Unit</v>
+      </c>
+      <c r="I2" t="str">
         <v>A</v>
       </c>
-      <c r="I2">
-        <v>10</v>
-      </c>
       <c r="J2">
-        <v>20</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Programming Languages</v>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>30</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Introduction</v>
       </c>
     </row>
     <row r="3">
@@ -474,34 +480,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Which of these is the official mascot of the Linux operating system (Tux)?</v>
+        <v>beginner</v>
       </c>
       <c r="C3" t="str">
+        <v>Which of the following is the official logo of the Python programming language?</v>
+      </c>
+      <c r="D3" t="str">
         <v/>
       </c>
-      <c r="D3" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/f/fa/Apple_logo_black.svg</v>
-      </c>
       <c r="E3" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/3/35/Tux.svg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/c/c3/Python-logo-notext.svg</v>
       </c>
       <c r="F3" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/8/87/Windows_logo_-_2021.svg</v>
+        <v>https://upload.wikimedia.org/wikipedia/en/3/30/Java_programming_language_logo.svg</v>
       </c>
       <c r="G3" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/d/d7/Android_robot.svg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/6/6a/JavaScript-logo.png</v>
       </c>
       <c r="H3" t="str">
-        <v>B</v>
-      </c>
-      <c r="I3">
+        <v>https://upload.wikimedia.org/wikipedia/commons/2/27/PHP-logo.svg</v>
+      </c>
+      <c r="I3" t="str">
+        <v>A</v>
+      </c>
+      <c r="J3">
         <v>10</v>
       </c>
-      <c r="J3">
-        <v>20</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Operating Systems</v>
+      <c r="K3">
+        <v>20</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Programming Languages</v>
       </c>
     </row>
     <row r="4">
@@ -509,34 +518,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Which of the following is the official logo of the React library?</v>
+        <v>beginner</v>
       </c>
       <c r="C4" t="str">
+        <v>Which of these is the official mascot of the Linux operating system (Tux)?</v>
+      </c>
+      <c r="D4" t="str">
         <v/>
       </c>
-      <c r="D4" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/9/95/Vue.js_Logo_2.svg</v>
-      </c>
       <c r="E4" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/c/cf/Angular_full_color_logo.svg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/f/fa/Apple_logo_black.svg</v>
       </c>
       <c r="F4" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/a/a7/React-icon.svg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/3/35/Tux.svg</v>
       </c>
       <c r="G4" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/1/1b/Svelte_Logo.svg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/8/87/Windows_logo_-_2021.svg</v>
       </c>
       <c r="H4" t="str">
-        <v>C</v>
-      </c>
-      <c r="I4">
+        <v>https://upload.wikimedia.org/wikipedia/commons/d/d7/Android_robot.svg</v>
+      </c>
+      <c r="I4" t="str">
+        <v>B</v>
+      </c>
+      <c r="J4">
         <v>10</v>
       </c>
-      <c r="J4">
-        <v>20</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Web Tech</v>
+      <c r="K4">
+        <v>20</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Operating Systems</v>
       </c>
     </row>
     <row r="5">
@@ -544,34 +556,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Identify the logo of the Git version control system:</v>
+        <v>beginner</v>
       </c>
       <c r="C5" t="str">
+        <v>Which of the following is the official logo of the React library?</v>
+      </c>
+      <c r="D5" t="str">
         <v/>
       </c>
-      <c r="D5" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/e/e0/Git-logo.svg</v>
-      </c>
       <c r="E5" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/4/4e/Docker_%28container_engine%29_logo.svg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/9/95/Vue.js_Logo_2.svg</v>
       </c>
       <c r="F5" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/3/39/Kubernetes_logo_without_workmark.svg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/c/cf/Angular_full_color_logo.svg</v>
       </c>
       <c r="G5" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/e/e9/Jenkins_logo.svg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/a/a7/React-icon.svg</v>
       </c>
       <c r="H5" t="str">
-        <v>A</v>
-      </c>
-      <c r="I5">
+        <v>https://upload.wikimedia.org/wikipedia/commons/1/1b/Svelte_Logo.svg</v>
+      </c>
+      <c r="I5" t="str">
+        <v>C</v>
+      </c>
+      <c r="J5">
         <v>10</v>
       </c>
-      <c r="J5">
-        <v>20</v>
-      </c>
-      <c r="K5" t="str">
-        <v>DevOps &amp; Tools</v>
+      <c r="K5">
+        <v>20</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Web Tech</v>
       </c>
     </row>
     <row r="6">
@@ -579,34 +594,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Look at the logo below. Which containerization platform does it represent?</v>
+        <v>intermediate</v>
       </c>
       <c r="C6" t="str">
+        <v>Identify the logo of the Git version control system:</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/e/e0/Git-logo.svg</v>
+      </c>
+      <c r="F6" t="str">
         <v>https://upload.wikimedia.org/wikipedia/commons/4/4e/Docker_%28container_engine%29_logo.svg</v>
       </c>
-      <c r="D6" t="str">
-        <v>Docker</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Podman</v>
-      </c>
-      <c r="F6" t="str">
-        <v>VirtualBox</v>
-      </c>
       <c r="G6" t="str">
-        <v>VMware</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/3/39/Kubernetes_logo_without_workmark.svg</v>
       </c>
       <c r="H6" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/e/e9/Jenkins_logo.svg</v>
+      </c>
+      <c r="I6" t="str">
         <v>A</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>15</v>
       </c>
-      <c r="J6">
-        <v>20</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Cloud &amp; DevOps</v>
+      <c r="K6">
+        <v>20</v>
+      </c>
+      <c r="L6" t="str">
+        <v>DevOps &amp; Tools</v>
       </c>
     </row>
     <row r="7">
@@ -614,34 +632,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Which of the following is the logo of PostgreSQL (Elephant)?</v>
+        <v>intermediate</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>Look at the logo below. Which containerization platform does it represent?</v>
       </c>
       <c r="D7" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/en/d/dd/MySQL_logo.svg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/4/4e/Docker_%28container_engine%29_logo.svg</v>
       </c>
       <c r="E7" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/9/93/MongoDB_Logo.svg</v>
+        <v>Docker</v>
       </c>
       <c r="F7" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/en/6/6b/Redis_Logo.svg</v>
+        <v>Podman</v>
       </c>
       <c r="G7" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/2/29/Postgresql_elephant.svg</v>
+        <v>VirtualBox</v>
       </c>
       <c r="H7" t="str">
-        <v>D</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
+        <v>VMware</v>
+      </c>
+      <c r="I7" t="str">
+        <v>A</v>
       </c>
       <c r="J7">
-        <v>20</v>
-      </c>
-      <c r="K7" t="str">
-        <v>Databases</v>
+        <v>15</v>
+      </c>
+      <c r="K7">
+        <v>20</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Cloud &amp; DevOps</v>
       </c>
     </row>
     <row r="8">
@@ -649,34 +670,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Identify the modern programming language represented by this mascot (Ferris):</v>
+        <v>intermediate</v>
       </c>
       <c r="C8" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/0/0f/Original_Ferris.svg</v>
+        <v>Which of the following is the logo of PostgreSQL (Elephant)?</v>
       </c>
       <c r="D8" t="str">
-        <v>Rust</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>Golang</v>
+        <v>https://upload.wikimedia.org/wikipedia/en/d/dd/MySQL_logo.svg</v>
       </c>
       <c r="F8" t="str">
-        <v>C++</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/9/93/MongoDB_Logo.svg</v>
       </c>
       <c r="G8" t="str">
-        <v>Zig</v>
+        <v>https://upload.wikimedia.org/wikipedia/en/6/6b/Redis_Logo.svg</v>
       </c>
       <c r="H8" t="str">
-        <v>A</v>
-      </c>
-      <c r="I8">
+        <v>https://upload.wikimedia.org/wikipedia/commons/2/29/Postgresql_elephant.svg</v>
+      </c>
+      <c r="I8" t="str">
+        <v>D</v>
+      </c>
+      <c r="J8">
         <v>15</v>
       </c>
-      <c r="J8">
-        <v>20</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Programming Languages</v>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Databases</v>
       </c>
     </row>
     <row r="9">
@@ -684,34 +708,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Which of the following is the official logo of GitHub (Octocat)?</v>
+        <v>advanced</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>Identify the modern programming language represented by this mascot (Ferris):</v>
       </c>
       <c r="D9" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/e/e1/GitLab_logo.svg</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/0/0f/Original_Ferris.svg</v>
       </c>
       <c r="E9" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/9/91/Octicons-mark-github.svg</v>
+        <v>Rust</v>
       </c>
       <c r="F9" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/0/0e/Bitbucket-blue-logomark-only.svg</v>
+        <v>Golang</v>
       </c>
       <c r="G9" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/0/02/Stack_Overflow_logo.svg</v>
+        <v>C++</v>
       </c>
       <c r="H9" t="str">
-        <v>B</v>
-      </c>
-      <c r="I9">
-        <v>10</v>
+        <v>Zig</v>
+      </c>
+      <c r="I9" t="str">
+        <v>A</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
-      <c r="K9" t="str">
-        <v>Developer Platforms</v>
+      <c r="K9">
+        <v>20</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Programming Languages</v>
       </c>
     </row>
     <row r="10">
@@ -719,34 +746,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Which popular JavaScript runtime uses this hexagonal green logo?</v>
+        <v>advanced</v>
       </c>
       <c r="C10" t="str">
-        <v>https://upload.wikimedia.org/wikipedia/commons/d/d9/Node.js_logo.svg</v>
+        <v>Which of the following is the official logo of GitHub (Octocat)?</v>
       </c>
       <c r="D10" t="str">
-        <v>Deno</v>
+        <v/>
       </c>
       <c r="E10" t="str">
-        <v>Node.js</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/e/e1/GitLab_logo.svg</v>
       </c>
       <c r="F10" t="str">
-        <v>Bun</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/9/91/Octicons-mark-github.svg</v>
       </c>
       <c r="G10" t="str">
-        <v>Electron</v>
+        <v>https://upload.wikimedia.org/wikipedia/commons/0/0e/Bitbucket-blue-logomark-only.svg</v>
       </c>
       <c r="H10" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/0/02/Stack_Overflow_logo.svg</v>
+      </c>
+      <c r="I10" t="str">
         <v>B</v>
       </c>
-      <c r="I10">
-        <v>10</v>
-      </c>
       <c r="J10">
         <v>20</v>
       </c>
-      <c r="K10" t="str">
-        <v>Web Tech</v>
+      <c r="K10">
+        <v>20</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Developer Platforms</v>
       </c>
     </row>
     <row r="11">
@@ -754,39 +784,80 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
+        <v>advanced</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Which popular JavaScript runtime uses this hexagonal green logo?</v>
+      </c>
+      <c r="D11" t="str">
+        <v>https://upload.wikimedia.org/wikipedia/commons/d/d9/Node.js_logo.svg</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Deno</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Node.js</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Bun</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Electron</v>
+      </c>
+      <c r="I11" t="str">
+        <v>B</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11">
+        <v>20</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Web Tech</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>advanced</v>
+      </c>
+      <c r="C12" t="str">
         <v>Which of the following is the official cryptocurrency logo of Ethereum?</v>
       </c>
-      <c r="C11" t="str">
+      <c r="D12" t="str">
         <v/>
       </c>
-      <c r="D11" t="str">
+      <c r="E12" t="str">
         <v>https://upload.wikimedia.org/wikipedia/commons/4/46/Bitcoin.svg</v>
       </c>
-      <c r="E11" t="str">
+      <c r="F12" t="str">
         <v>https://upload.wikimedia.org/wikipedia/commons/0/05/Ethereum_logo_2014.svg</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G12" t="str">
         <v>https://upload.wikimedia.org/wikipedia/commons/e/e9/Solana_logo.svg</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H12" t="str">
         <v>https://upload.wikimedia.org/wikipedia/en/d/d0/Dogecoin_Logo.png</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I12" t="str">
         <v>B</v>
       </c>
-      <c r="I11">
-        <v>15</v>
-      </c>
-      <c r="J11">
-        <v>20</v>
-      </c>
-      <c r="K11" t="str">
+      <c r="J12">
+        <v>20</v>
+      </c>
+      <c r="K12">
+        <v>20</v>
+      </c>
+      <c r="L12" t="str">
         <v>Blockchain &amp; Web3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>